--- a/input_orders.xlsx
+++ b/input_orders.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B910AF8-AED0-493D-B913-66D5471BE120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92751A51-7BC2-4A55-B3CC-0B0A4DE99580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="订单输入" sheetId="1" r:id="rId1"/>
+    <sheet name="插单输入" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>订单</t>
   </si>
@@ -34,39 +35,67 @@
     <t>最晚完工</t>
   </si>
   <si>
+    <t>公版</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>至上</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>订单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>插单日期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最早开工</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最晚完工</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>直采</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>富图勒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶樱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>嘉泰盛</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>富图勒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>公版</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>焕东</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>意诚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>环晟</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶顺</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>兴投</t>
+    <t>富图勒H</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>光恩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶樱D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉泰盛K</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -77,7 +106,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -98,6 +127,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -130,14 +166,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -145,6 +178,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -314,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
@@ -335,154 +381,219 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2">
+        <v>9000000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2">
+        <v>8800000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>2300000</v>
-      </c>
-      <c r="C2" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="B7" s="9">
+        <v>8300000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.65" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="9">
+        <v>15000000</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="22.65" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9">
+        <v>5000000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.5">
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1400000</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.5">
+      <c r="A12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46082</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65954875-C545-4907-A8CE-FE729A8CE728}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="3" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.5">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
-        <v>3000000</v>
-      </c>
-      <c r="C3" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3">
-        <v>3800000</v>
-      </c>
-      <c r="C4" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>5700000</v>
-      </c>
-      <c r="C5" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3">
-        <v>12000000</v>
-      </c>
-      <c r="C6" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
-        <v>6300000</v>
-      </c>
-      <c r="C7" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D7" s="4">
-        <v>46156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3">
-        <v>10000000</v>
-      </c>
-      <c r="C8" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="3">
-        <v>6000000</v>
-      </c>
-      <c r="C9" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D9" s="4">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="22.65" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3">
-        <v>77000000</v>
-      </c>
-      <c r="C10" s="4">
-        <v>46143</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="5"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="16.5">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="16.5">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="16.5">
-      <c r="A14" s="5"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/input_orders.xlsx
+++ b/input_orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92751A51-7BC2-4A55-B3CC-0B0A4DE99580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5486550-094D-4FF2-80EE-2AAD1DEA778C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>订单</t>
   </si>
@@ -63,39 +63,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>直采</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>富图勒</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>晶樱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>嘉泰盛</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>富图勒H</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>光恩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶樱D</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉泰盛K</t>
+    <t>焕东</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>意诚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶顺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>环晟</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴投</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -166,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -187,12 +179,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -382,157 +368,141 @@
     </row>
     <row r="2" spans="1:4" ht="14.65" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2">
-        <v>9000000</v>
+        <v>2300000</v>
       </c>
       <c r="C2" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D2" s="3">
-        <v>46091</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.65" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>3000000</v>
       </c>
       <c r="C3" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D3" s="3">
-        <v>46095</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.65" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2">
-        <v>5000000</v>
+        <v>3800000</v>
       </c>
       <c r="C4" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D4" s="3">
-        <v>46095</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.65" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>8800000</v>
+        <v>5700000</v>
       </c>
       <c r="C5" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D5" s="3">
-        <v>46098</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.65" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2">
-        <v>6000000</v>
+        <v>10000000</v>
       </c>
       <c r="C6" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D6" s="3">
-        <v>46100</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9">
-        <v>8300000</v>
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6300000</v>
       </c>
       <c r="C7" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D7" s="3">
-        <v>46103</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.65" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2">
-        <v>10000000</v>
+        <v>12000000</v>
       </c>
       <c r="C8" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D8" s="3">
-        <v>46107</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9">
-        <v>15000000</v>
+      <c r="A9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>77000000</v>
       </c>
       <c r="C9" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D9" s="3">
-        <v>46112</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22.65" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="9">
-        <v>5000000</v>
+      <c r="B10" s="2">
+        <v>6000000</v>
       </c>
       <c r="C10" s="3">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D10" s="3">
-        <v>46112</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9">
-        <v>1400000</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46082</v>
-      </c>
-      <c r="D11" s="3">
-        <v>46112</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="16.5">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="C12" s="3">
-        <v>46082</v>
-      </c>
-      <c r="D12" s="3">
-        <v>46112</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="16.5">
       <c r="A13" s="4"/>

--- a/input_orders.xlsx
+++ b/input_orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5486550-094D-4FF2-80EE-2AAD1DEA778C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DA5D6F-54AB-4311-A012-972892BF6D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>订单</t>
   </si>
@@ -35,14 +35,6 @@
     <t>最晚完工</t>
   </si>
   <si>
-    <t>公版</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>至上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>订单</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -63,31 +55,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>富图勒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉泰盛</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>焕东</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>意诚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶顺</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>环晟</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>兴投</t>
+    <t>A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -368,30 +352,30 @@
     </row>
     <row r="2" spans="1:4" ht="14.65" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>2300000</v>
+        <v>6210000</v>
       </c>
       <c r="C2" s="3">
         <v>46143</v>
       </c>
       <c r="D2" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.65" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>3000000</v>
+        <v>6210000</v>
       </c>
       <c r="C3" s="3">
         <v>46143</v>
       </c>
       <c r="D3" s="3">
-        <v>46148</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.65" customHeight="1">
@@ -399,104 +383,66 @@
         <v>11</v>
       </c>
       <c r="B4" s="2">
-        <v>3800000</v>
+        <v>4140000</v>
       </c>
       <c r="C4" s="3">
         <v>46143</v>
       </c>
       <c r="D4" s="3">
-        <v>46149</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.65" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>5700000</v>
+        <v>4140000</v>
       </c>
       <c r="C5" s="3">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="D5" s="3">
-        <v>46149</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.65" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>10000000</v>
+        <v>4140000</v>
       </c>
       <c r="C6" s="3">
         <v>46143</v>
       </c>
       <c r="D6" s="3">
-        <v>46156</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2">
-        <v>6300000</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D7" s="3">
-        <v>46156</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D8" s="3">
-        <v>46157</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="16.5">
-      <c r="A9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2">
-        <v>77000000</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D9" s="3">
-        <v>46173</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="22.65" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46143</v>
-      </c>
-      <c r="D10" s="3">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="16.5">
       <c r="A12" s="4"/>
@@ -539,19 +485,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5">
       <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">

--- a/input_orders.xlsx
+++ b/input_orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DA5D6F-54AB-4311-A012-972892BF6D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30C23C6-E519-4796-A249-8B77EBBC480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>订单</t>
   </si>
@@ -72,6 +72,18 @@
   </si>
   <si>
     <t>E</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -142,7 +154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +175,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -355,7 +368,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>6210000</v>
+        <v>12420000</v>
       </c>
       <c r="C2" s="3">
         <v>46143</v>
@@ -369,13 +382,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="2">
-        <v>6210000</v>
+        <v>16560000</v>
       </c>
       <c r="C3" s="3">
         <v>46143</v>
       </c>
       <c r="D3" s="3">
-        <v>46150</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.65" customHeight="1">
@@ -383,13 +396,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="2">
-        <v>4140000</v>
+        <v>24840000</v>
       </c>
       <c r="C4" s="3">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="D4" s="3">
-        <v>46145</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.65" customHeight="1">
@@ -397,13 +410,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>4140000</v>
+        <v>13800000</v>
       </c>
       <c r="C5" s="3">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="D5" s="3">
-        <v>46150</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.65" customHeight="1">
@@ -411,26 +424,42 @@
         <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>4140000</v>
+        <v>9660000</v>
       </c>
       <c r="C6" s="3">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="D6" s="3">
-        <v>46150</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2">
+        <v>8280000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46160</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46170</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="14.65" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
+        <v>11040000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46166</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46173</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="16.5">
       <c r="A9" s="4"/>
@@ -480,6 +509,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -501,15 +531,38 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="7"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="A2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="8">
+        <v>11040000</v>
+      </c>
+      <c r="C2" s="6">
+        <v>46156</v>
+      </c>
+      <c r="D2" s="6">
+        <v>46157</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46164</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>4140000</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46156</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46157</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46167</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/input_orders.xlsx
+++ b/input_orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\cp_sat_scheduler_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30C23C6-E519-4796-A249-8B77EBBC480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B95008-C8B3-4B36-B80F-6595D0455393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="订单输入" sheetId="1" r:id="rId1"/>
@@ -374,7 +374,7 @@
         <v>46143</v>
       </c>
       <c r="D2" s="3">
-        <v>46150</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.65" customHeight="1">
@@ -385,10 +385,10 @@
         <v>16560000</v>
       </c>
       <c r="C3" s="3">
-        <v>46143</v>
+        <v>46145</v>
       </c>
       <c r="D3" s="3">
-        <v>46154</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.65" customHeight="1">
@@ -399,10 +399,10 @@
         <v>24840000</v>
       </c>
       <c r="C4" s="3">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D4" s="3">
-        <v>46167</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.65" customHeight="1">
@@ -410,13 +410,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>13800000</v>
+        <v>16560000</v>
       </c>
       <c r="C5" s="3">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="D5" s="3">
-        <v>46164</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.65" customHeight="1">
@@ -424,13 +424,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="2">
-        <v>9660000</v>
+        <v>12420000</v>
       </c>
       <c r="C6" s="3">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="D6" s="3">
-        <v>46171</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.65" customHeight="1">
@@ -438,10 +438,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="2">
-        <v>8280000</v>
+        <v>16560000</v>
       </c>
       <c r="C7" s="3">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D7" s="3">
         <v>46170</v>
@@ -452,7 +452,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2">
-        <v>11040000</v>
+        <v>12420000</v>
       </c>
       <c r="C8" s="3">
         <v>46166</v>
@@ -532,33 +532,33 @@
     </row>
     <row r="2" spans="1:5" ht="16.5">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B2" s="8">
-        <v>11040000</v>
+        <v>8280000</v>
       </c>
       <c r="C2" s="6">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="D2" s="6">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="E2" s="6">
-        <v>46164</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>4140000</v>
       </c>
       <c r="C3" s="6">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="D3" s="6">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="E3" s="6">
         <v>46167</v>
